--- a/examples/output/MNL_swissmetro_WTP.xlsx
+++ b/examples/output/MNL_swissmetro_WTP.xlsx
@@ -440,7 +440,7 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0.2205295960664235</v>
+        <v>0.22052959606642353</v>
       </c>
       <c r="C2">
         <v>0.05352240281580143</v>
@@ -455,7 +455,7 @@
         <v>0.06368025247022238</v>
       </c>
       <c r="G2">
-        <v>3.4630766605321748</v>
+        <v>3.463076660532175</v>
       </c>
       <c r="H2">
         <v>0.0005340362199897086</v>
@@ -478,10 +478,10 @@
         <v>0.0</v>
       </c>
       <c r="F3">
-        <v>0.10173309609633123</v>
+        <v>0.1017330960963312</v>
       </c>
       <c r="G3">
-        <v>11.589793556994707</v>
+        <v>11.58979355699471</v>
       </c>
       <c r="H3">
         <v>0.0</v>
